--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
@@ -864,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,25 @@
     <t>AQUINO</t>
   </si>
   <si>
+    <t>PALMA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
   </si>
   <si>
     <t>MICHEL</t>
@@ -609,16 +618,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,16 +644,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.17</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,16 +670,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -720,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H2">
         <v>8.5</v>
@@ -746,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>82.93000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,7 +799,7 @@
         <v>94.44</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -829,10 +847,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -846,24 +864,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920048</v>
+        <v>21330051920242</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920048</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,28 +76,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PALMA</t>
+  </si>
+  <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>PALMA</t>
+    <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RANGEL</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>BETSI JOSELIN</t>
   </si>
   <si>
-    <t>ROBERTO</t>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>MICHEL</t>
@@ -809,7 +818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,22 +850,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920032</v>
+        <v>21330051920242</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -864,39 +873,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920242</v>
+        <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920048</v>
+        <v>21330051920038</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -905,6 +914,29 @@
         <v>11</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920048</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,40 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PALMA</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
+    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
   </si>
 </sst>
 </file>
@@ -747,16 +726,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>86.48999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -773,16 +752,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -850,22 +829,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920242</v>
+        <v>21330051920057</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -879,10 +858,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -891,52 +870,6 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920038</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920048</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20212.xlsx
@@ -76,19 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
     <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
   </si>
 </sst>
 </file>
@@ -829,7 +829,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920057</v>
+        <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920032</v>
+        <v>21330051920057</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
